--- a/tools/templates/point_template.xlsx
+++ b/tools/templates/point_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/d36616b/Documents/git/integrated-automation/nexuscon-2025/tools/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525683FD-911C-2F4D-BBFB-1AD0D488C086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532408DC-387D-D34A-88D3-A45C8D22E1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20300" yWindow="-28300" windowWidth="34400" windowHeight="28300" xr2:uid="{1DAAB171-EED9-CD41-A923-E922B19884F4}"/>
+    <workbookView xWindow="-20280" yWindow="-28300" windowWidth="34400" windowHeight="28300" xr2:uid="{1DAAB171-EED9-CD41-A923-E922B19884F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Switch" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
     <t>Physical switch to toggle on/off connected LED</t>
   </si>
   <si>
-    <t>Test LED</t>
+    <t>LED that will toggle on/of with a physical switch</t>
   </si>
 </sst>
 </file>
@@ -832,7 +832,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>24</v>
       </c>

--- a/tools/templates/point_template.xlsx
+++ b/tools/templates/point_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/d36616b/Documents/git/integrated-automation/nexuscon-2025/tools/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532408DC-387D-D34A-88D3-A45C8D22E1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9381E500-B78C-0A45-9EA3-5E0425268CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20280" yWindow="-28300" windowWidth="34400" windowHeight="28300" xr2:uid="{1DAAB171-EED9-CD41-A923-E922B19884F4}"/>
   </bookViews>
@@ -98,18 +98,12 @@
     <t>AO</t>
   </si>
   <si>
-    <t>%</t>
-  </si>
-  <si>
     <t>BI</t>
   </si>
   <si>
     <t>Boolean</t>
   </si>
   <si>
-    <t>FALSE,TRUE</t>
-  </si>
-  <si>
     <t>LEDOutput</t>
   </si>
   <si>
@@ -120,6 +114,12 @@
   </si>
   <si>
     <t>LED that will toggle on/of with a physical switch</t>
+  </si>
+  <si>
+    <t>PERCENT</t>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
   </si>
 </sst>
 </file>
@@ -834,10 +834,10 @@
     </row>
     <row r="2" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>13</v>
@@ -849,7 +849,7 @@
         <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G2" s="2">
         <v>1</v>
@@ -875,22 +875,22 @@
     </row>
     <row r="3" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G3" s="2">
         <v>1</v>

--- a/tools/templates/point_template.xlsx
+++ b/tools/templates/point_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/d36616b/Documents/git/integrated-automation/nexuscon-2025/tools/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9381E500-B78C-0A45-9EA3-5E0425268CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB21F4A-A584-9349-9B9A-7FBB34D7DE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20280" yWindow="-28300" windowWidth="34400" windowHeight="28300" xr2:uid="{1DAAB171-EED9-CD41-A923-E922B19884F4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>POINT NAME</t>
   </si>
@@ -56,9 +56,6 @@
     <t>UNITS</t>
   </si>
   <si>
-    <t>QUANTITY</t>
-  </si>
-  <si>
     <t>TREND</t>
   </si>
   <si>
@@ -98,12 +95,18 @@
     <t>AO</t>
   </si>
   <si>
+    <t>%</t>
+  </si>
+  <si>
     <t>BI</t>
   </si>
   <si>
     <t>Boolean</t>
   </si>
   <si>
+    <t>FALSE,TRUE</t>
+  </si>
+  <si>
     <t>LEDOutput</t>
   </si>
   <si>
@@ -114,12 +117,6 @@
   </si>
   <si>
     <t>LED that will toggle on/of with a physical switch</t>
-  </si>
-  <si>
-    <t>PERCENT</t>
-  </si>
-  <si>
-    <t>BOOLEAN</t>
   </si>
 </sst>
 </file>
@@ -291,7 +288,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="12">
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -375,19 +372,6 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
         <bottom/>
         <vertical/>
         <horizontal/>
@@ -435,16 +419,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{31EBBF34-329A-C64D-94D3-3A246B82A98F}" name="Table1" displayName="Table1" ref="A1:M3" totalsRowShown="0" tableBorderDxfId="12">
-  <autoFilter ref="A1:M3" xr:uid="{31EBBF34-329A-C64D-94D3-3A246B82A98F}"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{31EBBF34-329A-C64D-94D3-3A246B82A98F}" name="Table1" displayName="Table1" ref="A1:L3" totalsRowShown="0" tableBorderDxfId="11">
+  <autoFilter ref="A1:L3" xr:uid="{31EBBF34-329A-C64D-94D3-3A246B82A98F}"/>
+  <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{DF800DE3-8ACA-0544-831A-458B65B779D7}" name="POINT NAME"/>
-    <tableColumn id="2" xr3:uid="{302A0025-0B2C-5E47-B790-2A5E1497E596}" name="POINT DESCRIPTION" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{93123404-8666-FF4C-9047-388F85519FFE}" name="HARDWARE/SOFTWARE" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{62FD709F-81D6-8C4A-A3B6-1AE7E57ADB36}" name="POINT TYPE" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{294ADF25-DA1A-3446-9D3F-BA3072337C82}" name="VALUE TYPE" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{1B3E44AA-B14E-6649-B331-97051CEA939D}" name="UNITS" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{F690922F-DD10-8342-873D-4135C7EBB1D4}" name="QUANTITY" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{302A0025-0B2C-5E47-B790-2A5E1497E596}" name="POINT DESCRIPTION" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{93123404-8666-FF4C-9047-388F85519FFE}" name="HARDWARE/SOFTWARE" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{62FD709F-81D6-8C4A-A3B6-1AE7E57ADB36}" name="POINT TYPE" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{294ADF25-DA1A-3446-9D3F-BA3072337C82}" name="VALUE TYPE" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{1B3E44AA-B14E-6649-B331-97051CEA939D}" name="UNITS" dataDxfId="6"/>
     <tableColumn id="8" xr3:uid="{63D5CA62-D86C-FB48-AF00-81DBF0254B75}" name="TREND" dataDxfId="5"/>
     <tableColumn id="9" xr3:uid="{5AEE3091-F354-034C-AD7F-B3B64E60157E}" name="COV/INTERVAL" dataDxfId="4"/>
     <tableColumn id="10" xr3:uid="{A3EBC828-36FD-EC48-AFBC-B382C1E4E3B1}" name="ALARM" dataDxfId="3"/>
@@ -773,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E43971F-072A-D142-B76B-0C3BD3F19F45}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
@@ -781,17 +764,16 @@
     <col min="3" max="3" width="21.33203125" customWidth="1"/>
     <col min="4" max="4" width="12.33203125" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.1640625" customWidth="1"/>
-    <col min="8" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
-    <col min="13" max="13" width="38.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="38.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -810,78 +792,72 @@
       <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="4">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="12" t="s">
+    <row r="3" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="2">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="4">
-        <v>2</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="34" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>24</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>20</v>
@@ -890,24 +866,21 @@
         <v>21</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="2">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>18</v>
+      <c r="I3" s="5"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
